--- a/システム開発演習/020-内部_プログラミング設計/021-クラス図/021-クラス図_商品検索画面.xlsx
+++ b/システム開発演習/020-内部_プログラミング設計/021-クラス図/021-クラス図_商品検索画面.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\システム開発演習\020-内部_プログラミング設計\021-クラス図\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F022C2C2-DAD5-4F8D-8A90-B82EF3A1B84E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A061FE-DB57-473B-A6A9-90C33C193E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>システム名称</t>
     <rPh sb="4" eb="6">
@@ -206,6 +206,27 @@
     <t>株式会社XYZ</t>
     <rPh sb="0" eb="4">
       <t>カブシキガイシャ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>髙木日向子</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>クラス図</t>
+    <rPh sb="3" eb="4">
+      <t>ズ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>アスリ指摘修正</t>
+    <rPh sb="3" eb="5">
+      <t>シテキ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シュウセイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -806,7 +827,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1030,6 +1051,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1102,7 +1126,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="37" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1244,22 +1268,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>182879</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>184354</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>165919</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>49</xdr:col>
-      <xdr:colOff>172690</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>104467</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>14352</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
+        <xdr:cNvPr id="6" name="図 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A9F5AA0-3965-4CA9-989A-7591D6A3F211}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{827E3EF9-1059-431D-8220-8FD2961B8430}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1275,8 +1299,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="182879" y="1234440"/>
-          <a:ext cx="8958551" cy="4053840"/>
+          <a:off x="184354" y="1235177"/>
+          <a:ext cx="8037871" cy="3517094"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4628,12 +4652,12 @@
         <v>1</v>
       </c>
       <c r="B5" s="78"/>
-      <c r="C5" s="103">
+      <c r="C5" s="79">
         <v>45566</v>
       </c>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
       <c r="G5" s="78" t="s">
         <v>23</v>
       </c>
@@ -4693,15 +4717,21 @@
         <v>2</v>
       </c>
       <c r="B6" s="65"/>
-      <c r="C6" s="66"/>
-      <c r="D6" s="66"/>
-      <c r="E6" s="66"/>
-      <c r="F6" s="66"/>
-      <c r="G6" s="65"/>
+      <c r="C6" s="104">
+        <v>45572</v>
+      </c>
+      <c r="D6" s="104"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="104"/>
+      <c r="G6" s="65" t="s">
+        <v>25</v>
+      </c>
       <c r="H6" s="65"/>
       <c r="I6" s="65"/>
       <c r="J6" s="65"/>
-      <c r="K6" s="65"/>
+      <c r="K6" s="65" t="s">
+        <v>26</v>
+      </c>
       <c r="L6" s="65"/>
       <c r="M6" s="65"/>
       <c r="N6" s="65"/>
@@ -4711,7 +4741,9 @@
       <c r="R6" s="65"/>
       <c r="S6" s="65"/>
       <c r="T6" s="65"/>
-      <c r="U6" s="65"/>
+      <c r="U6" s="65" t="s">
+        <v>27</v>
+      </c>
       <c r="V6" s="65"/>
       <c r="W6" s="65"/>
       <c r="X6" s="65"/>
@@ -7263,157 +7295,157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:51" customFormat="1" ht="14.25" customHeight="1" thickTop="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
-      <c r="P1" s="82"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
-      <c r="S1" s="83"/>
-      <c r="T1" s="97" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="84"/>
+      <c r="T1" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="U1" s="97"/>
-      <c r="V1" s="97"/>
-      <c r="W1" s="97"/>
-      <c r="X1" s="98"/>
-      <c r="Y1" s="98"/>
-      <c r="Z1" s="98"/>
-      <c r="AA1" s="98"/>
-      <c r="AB1" s="98"/>
-      <c r="AC1" s="98"/>
-      <c r="AD1" s="98"/>
-      <c r="AE1" s="98"/>
-      <c r="AF1" s="98"/>
-      <c r="AG1" s="98"/>
-      <c r="AH1" s="97" t="s">
+      <c r="U1" s="98"/>
+      <c r="V1" s="98"/>
+      <c r="W1" s="98"/>
+      <c r="X1" s="99"/>
+      <c r="Y1" s="99"/>
+      <c r="Z1" s="99"/>
+      <c r="AA1" s="99"/>
+      <c r="AB1" s="99"/>
+      <c r="AC1" s="99"/>
+      <c r="AD1" s="99"/>
+      <c r="AE1" s="99"/>
+      <c r="AF1" s="99"/>
+      <c r="AG1" s="99"/>
+      <c r="AH1" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="AI1" s="97"/>
-      <c r="AJ1" s="97"/>
-      <c r="AK1" s="97"/>
-      <c r="AL1" s="99">
+      <c r="AI1" s="98"/>
+      <c r="AJ1" s="98"/>
+      <c r="AK1" s="98"/>
+      <c r="AL1" s="100">
         <v>45566</v>
       </c>
-      <c r="AM1" s="99"/>
-      <c r="AN1" s="99"/>
-      <c r="AO1" s="99"/>
-      <c r="AP1" s="99"/>
-      <c r="AQ1" s="99"/>
-      <c r="AR1" s="99"/>
-      <c r="AS1" s="99"/>
-      <c r="AT1" s="99"/>
-      <c r="AU1" s="87" t="s">
+      <c r="AM1" s="100"/>
+      <c r="AN1" s="100"/>
+      <c r="AO1" s="100"/>
+      <c r="AP1" s="100"/>
+      <c r="AQ1" s="100"/>
+      <c r="AR1" s="100"/>
+      <c r="AS1" s="100"/>
+      <c r="AT1" s="100"/>
+      <c r="AU1" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="AV1" s="88"/>
-      <c r="AW1" s="91">
+      <c r="AV1" s="89"/>
+      <c r="AW1" s="92">
         <v>1</v>
       </c>
-      <c r="AX1" s="92"/>
-      <c r="AY1" s="93"/>
+      <c r="AX1" s="93"/>
+      <c r="AY1" s="94"/>
     </row>
     <row r="2" spans="1:51" customFormat="1" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A2" s="84"/>
-      <c r="B2" s="85"/>
-      <c r="C2" s="85"/>
-      <c r="D2" s="85"/>
-      <c r="E2" s="85"/>
-      <c r="F2" s="85"/>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="85"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
-      <c r="O2" s="85"/>
-      <c r="P2" s="85"/>
-      <c r="Q2" s="85"/>
-      <c r="R2" s="85"/>
-      <c r="S2" s="86"/>
-      <c r="T2" s="100" t="s">
+      <c r="A2" s="85"/>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="86"/>
+      <c r="N2" s="86"/>
+      <c r="O2" s="86"/>
+      <c r="P2" s="86"/>
+      <c r="Q2" s="86"/>
+      <c r="R2" s="86"/>
+      <c r="S2" s="87"/>
+      <c r="T2" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="U2" s="100"/>
-      <c r="V2" s="100"/>
-      <c r="W2" s="100"/>
-      <c r="X2" s="101" t="s">
+      <c r="U2" s="101"/>
+      <c r="V2" s="101"/>
+      <c r="W2" s="101"/>
+      <c r="X2" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="Y2" s="101"/>
-      <c r="Z2" s="101"/>
-      <c r="AA2" s="101"/>
-      <c r="AB2" s="101"/>
-      <c r="AC2" s="101"/>
-      <c r="AD2" s="101"/>
-      <c r="AE2" s="101"/>
-      <c r="AF2" s="101"/>
-      <c r="AG2" s="101"/>
-      <c r="AH2" s="100" t="s">
+      <c r="Y2" s="102"/>
+      <c r="Z2" s="102"/>
+      <c r="AA2" s="102"/>
+      <c r="AB2" s="102"/>
+      <c r="AC2" s="102"/>
+      <c r="AD2" s="102"/>
+      <c r="AE2" s="102"/>
+      <c r="AF2" s="102"/>
+      <c r="AG2" s="102"/>
+      <c r="AH2" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="AI2" s="100"/>
-      <c r="AJ2" s="100"/>
-      <c r="AK2" s="100"/>
-      <c r="AL2" s="102" t="s">
+      <c r="AI2" s="101"/>
+      <c r="AJ2" s="101"/>
+      <c r="AK2" s="101"/>
+      <c r="AL2" s="103" t="s">
         <v>22</v>
       </c>
-      <c r="AM2" s="102"/>
-      <c r="AN2" s="102"/>
-      <c r="AO2" s="102"/>
-      <c r="AP2" s="102"/>
-      <c r="AQ2" s="102"/>
-      <c r="AR2" s="102"/>
-      <c r="AS2" s="102"/>
-      <c r="AT2" s="102"/>
-      <c r="AU2" s="89"/>
-      <c r="AV2" s="90"/>
-      <c r="AW2" s="94"/>
-      <c r="AX2" s="95"/>
-      <c r="AY2" s="96"/>
+      <c r="AM2" s="103"/>
+      <c r="AN2" s="103"/>
+      <c r="AO2" s="103"/>
+      <c r="AP2" s="103"/>
+      <c r="AQ2" s="103"/>
+      <c r="AR2" s="103"/>
+      <c r="AS2" s="103"/>
+      <c r="AT2" s="103"/>
+      <c r="AU2" s="90"/>
+      <c r="AV2" s="91"/>
+      <c r="AW2" s="95"/>
+      <c r="AX2" s="96"/>
+      <c r="AY2" s="97"/>
     </row>
     <row r="3" spans="1:51" ht="10.199999999999999" thickTop="1"/>
     <row r="4" spans="1:51">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="80" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="79"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="79"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:51" ht="10.199999999999999" thickBot="1">
-      <c r="A5" s="80"/>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
+      <c r="A5" s="81"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
     </row>
     <row r="6" spans="1:51" ht="13.5" customHeight="1">
       <c r="A6" s="26"/>
